--- a/Docs/KNOWLEDGE_BASE/REGISTRY/PROJECT_CANONICAL_DOMAIN_MAP.xlsx
+++ b/Docs/KNOWLEDGE_BASE/REGISTRY/PROJECT_CANONICAL_DOMAIN_MAP.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明" sheetId="1" r:id="R1e1dcbc560d6426b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据" sheetId="2" r:id="R3e7bde274022470e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明" sheetId="1" r:id="R8fdc57e8de314c0b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据" sheetId="2" r:id="R4e32f6a90044453b"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -575,8 +575,7 @@
         <x:v>记录数</x:v>
       </x:c>
       <x:c r="B2" s="7" t="n">
-        <x:f>COUNTA(A4:A5)</x:f>
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="30" customHeight="1">
@@ -628,6 +627,23 @@
       </x:c>
       <x:c r="E5" t="str">
         <x:v>追加V72智能决策、Arena、模型和后续缺口记录；既有行保持不变。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" t="str">
+        <x:v>PROJECT_CANONICAL_DOMAIN_MAP.xlsx</x:v>
+      </x:c>
+      <x:c r="B6" t="str">
+        <x:v>LUOYANG-184-T4-LIVING-WORLD-COMPLETION-MASTER-V1</x:v>
+      </x:c>
+      <x:c r="C6" t="n">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="D6" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E6" t="str">
+        <x:v>追加洛阳T4 Phase 0—19正式状态、完成证据与Deferred边界；既有行保持不变。</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -636,7 +652,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd946ce0a36af4534"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf7b0ed3d81d346a0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -689,8 +705,7 @@
         <x:v>记录数</x:v>
       </x:c>
       <x:c r="B2" s="7" t="n">
-        <x:f>COUNTA(A4:A46)</x:f>
-        <x:v>41</x:v>
+        <x:v>42</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="30" customHeight="1">
@@ -2481,13 +2496,156 @@
       <x:c r="T46" s="56"/>
       <x:c r="U46" s="56"/>
     </x:row>
+    <x:row r="47">
+      <x:c r="A47" t="str">
+        <x:v>LuoyangT4LivingWorld</x:v>
+      </x:c>
+      <x:c r="B47" t="str">
+        <x:v>AGENTS.md</x:v>
+      </x:c>
+      <x:c r="C47" t="str">
+        <x:v>Docs/WORLD_SIMULATION_FOUNDATION.md|Docs/SANDBOX_NPC_AI.md|Docs/TASK_M12_PERMANENT_POPULATION_AND_ATTENTION.md</x:v>
+      </x:c>
+      <x:c r="D47" t="str">
+        <x:v>Docs/GAME_SYSTEMS_MASTER_AND_STATUS.md</x:v>
+      </x:c>
+      <x:c r="E47" t="str">
+        <x:v>Docs/HISTORICAL_WORLD_REFERENCE/LUOYANG_184_T4_LIVING_WORLD_COMPLETION_MASTER_V1/LUOYANG_184_T4_LIVING_WORLD_COMPLETION_MASTER_V1_REPORT.md</x:v>
+      </x:c>
+      <x:c r="F47" t="str">
+        <x:v>Historical tax calibration and per-route gate recalculation remain deferred.</x:v>
+      </x:c>
+      <x:c r="G47" t="str">
+        <x:v>NO</x:v>
+      </x:c>
+      <x:c r="H47" t="str">
+        <x:v>Docs/TASK_LUOYANG_184_T4_LIVING_WORLD_COMPLETION_MASTER_V1.md</x:v>
+      </x:c>
+      <x:c r="I47" t="str">
+        <x:v>One Cell world, permanent-person identity, conservation and save compatibility remain authoritative.</x:v>
+      </x:c>
+      <x:c r="J47" t="str">
+        <x:v>domain.luoyang.t4.living-world.v1</x:v>
+      </x:c>
+      <x:c r="K47" t="str">
+        <x:v>Luoyang T4 Living World V1</x:v>
+      </x:c>
+      <x:c r="L47"/>
+      <x:c r="M47"/>
+      <x:c r="N47"/>
+      <x:c r="O47"/>
+      <x:c r="P47" t="str">
+        <x:v>COMPLETE_WITH_DEFERRED_ENHANCEMENTS</x:v>
+      </x:c>
+      <x:c r="Q47" t="str">
+        <x:v>400K Persons; 80,899 households; 2,084 opening facilities retained</x:v>
+      </x:c>
+      <x:c r="R47" t="str"/>
+      <x:c r="S47" t="str"/>
+      <x:c r="T47" t="str"/>
+      <x:c r="U47" t="str"/>
+    </x:row>
+    <x:row r="48">
+      <x:c r="A48" t="str">
+        <x:v>MapPresentation</x:v>
+      </x:c>
+      <x:c r="B48" t="str">
+        <x:v>AGENTS.md</x:v>
+      </x:c>
+      <x:c r="C48" t="str">
+        <x:v>Docs/TASK_LUOYANG_PLAYABLE_VERTICAL_SLICE_MAP_PRESENTATION_AND_CONSTRUCTION_ASSET_LIBRARY_V1.md</x:v>
+      </x:c>
+      <x:c r="D48" t="str">
+        <x:v>Docs/GAME_SYSTEMS_MASTER_AND_STATUS.md</x:v>
+      </x:c>
+      <x:c r="E48" t="str">
+        <x:v>Docs/HISTORICAL_WORLD_REFERENCE/LUOYANG_PLAYABLE_VERTICAL_SLICE_MAP_PRESENTATION_AND_CONSTRUCTION_ASSET_LIBRARY_V1/LUOYANG_PLAYABLE_VERTICAL_SLICE_MAP_PRESENTATION_AND_CONSTRUCTION_ASSET_LIBRARY_V1_REPORT.md</x:v>
+      </x:c>
+      <x:c r="F48" t="str"/>
+      <x:c r="G48" t="str"/>
+      <x:c r="H48" t="str">
+        <x:v>Docs/TASK_LUOYANG_PLAYABLE_VERTICAL_SLICE_MAP_PRESENTATION_AND_CONSTRUCTION_ASSET_LIBRARY_V1.md</x:v>
+      </x:c>
+      <x:c r="I48" t="str">
+        <x:v>Runtime Cell/Facility/Person/Shipment remains authoritative.</x:v>
+      </x:c>
+      <x:c r="J48" t="str">
+        <x:v>domain.map-presentation.v1</x:v>
+      </x:c>
+      <x:c r="K48" t="str">
+        <x:v>Unified Map Presentation and Construction Assets</x:v>
+      </x:c>
+      <x:c r="L48" t="str"/>
+      <x:c r="M48" t="str"/>
+      <x:c r="N48" t="str"/>
+      <x:c r="O48" t="str"/>
+      <x:c r="P48" t="str">
+        <x:v>GOLDEN_SLICE_PLAYABLE_PROCEDURAL_V1</x:v>
+      </x:c>
+      <x:c r="Q48" t="str"/>
+      <x:c r="R48" t="str"/>
+      <x:c r="S48" t="str"/>
+      <x:c r="T48" t="str"/>
+      <x:c r="U48" t="str">
+        <x:v>CURRENT</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49">
+      <x:c r="A49" t="str">
+        <x:v>GlobalSpatialFoundation</x:v>
+      </x:c>
+      <x:c r="B49" t="str">
+        <x:v>AGENTS.md</x:v>
+      </x:c>
+      <x:c r="C49" t="str">
+        <x:v>Docs/HISTORICAL_WORLD_REFERENCE/WORLD_GLOBAL_ORIGIN_CELL_GRID_AND_SPATIAL_CONTINUITY_V1/GLOBAL_SPATIAL_FOUNDATION_CONTRACT_V1.md</x:v>
+      </x:c>
+      <x:c r="D49" t="str">
+        <x:v>Docs/GAME_SYSTEMS_MASTER_AND_STATUS.md</x:v>
+      </x:c>
+      <x:c r="E49" t="str">
+        <x:v>Docs/HISTORICAL_WORLD_REFERENCE/WORLD_REGION_CELL_BOUNDARY_AND_TECHNICAL_BLOCK_SEMANTICS_CORRECTION_V1/WORLD_REGION_CELL_BOUNDARY_AND_TECHNICAL_BLOCK_SEMANTICS_CORRECTION_V1_REPORT.md</x:v>
+      </x:c>
+      <x:c r="F49" t="str">
+        <x:v>Terrain Tile and Streaming Unit sizes require real Unity benchmark; 河南尹 final Terrain remains unproduced.</x:v>
+      </x:c>
+      <x:c r="G49" t="str">
+        <x:v>NO</x:v>
+      </x:c>
+      <x:c r="H49" t="str">
+        <x:v>Docs/HISTORICAL_WORLD_REFERENCE/WORLD_GLOBAL_ORIGIN_CELL_GRID_AND_SPATIAL_CONTINUITY_V1/GLOBAL_SPATIAL_FOUNDATION_CONTRACT_V1.md</x:v>
+      </x:c>
+      <x:c r="I49" t="str">
+        <x:v>Global Cell membership defines Region; polygons and technical blocks cannot create, cut or renumber Cells.</x:v>
+      </x:c>
+      <x:c r="J49" t="str">
+        <x:v>domain.global-spatial-foundation.v1</x:v>
+      </x:c>
+      <x:c r="K49" t="str">
+        <x:v>One World One Global Grid</x:v>
+      </x:c>
+      <x:c r="L49"/>
+      <x:c r="M49"/>
+      <x:c r="N49"/>
+      <x:c r="O49"/>
+      <x:c r="P49" t="str">
+        <x:v>REGION_CELL_BOUNDARY_CONTRACT_FROZEN</x:v>
+      </x:c>
+      <x:c r="Q49"/>
+      <x:c r="R49"/>
+      <x:c r="S49"/>
+      <x:c r="T49"/>
+      <x:c r="U49" t="str">
+        <x:v>CURRENT</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:L1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6e041211bfd64f5c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb8f1d795095d4df6"/>
   </x:tableParts>
 </x:worksheet>
 </file>